--- a/samples/wildling/design-data/xlsx/Reward.xlsx
+++ b/samples/wildling/design-data/xlsx/Reward.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[RewardGroup!$B$2:$C$163]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[RewardEntry!$B$2:$J$374]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[RequirementGroup!$B$2:$C$42]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RequirementEntry!$B$2:$I$82]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[RequirementEntry!$B$2:$J$81]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[DropTable!$B$2:$E$20]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="486">
   <si>
     <t xml:space="preserve">:table RewardGroup</t>
   </si>
@@ -1324,6 +1324,9 @@
     <t xml:space="preserve">req.stage_id</t>
   </si>
   <si>
+    <t xml:space="preserve">req.percent</t>
+  </si>
+  <si>
     <t xml:space="preserve">foreign RequirementGroup</t>
   </si>
   <si>
@@ -1354,6 +1357,9 @@
     <t xml:space="preserve">요구 스테이지</t>
   </si>
   <si>
+    <t xml:space="preserve">요구 완성률. 백분율</t>
+  </si>
+  <si>
     <t xml:space="preserve">LevelRequirement</t>
   </si>
   <si>
@@ -1375,10 +1381,10 @@
     <t xml:space="preserve">weir_forest_18</t>
   </si>
   <si>
-    <t xml:space="preserve">Recorded</t>
-  </si>
-  <si>
     <t xml:space="preserve">salt_coast_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodexCompletionRequirement</t>
   </si>
   <si>
     <t xml:space="preserve">ashen_crater_18</t>
@@ -12014,18 +12020,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53.90625" customWidth="1"/>
     <col min="2" max="2" width="31.640625" customWidth="1"/>
     <col min="3" max="3" width="23.4375" customWidth="1"/>
-    <col min="4" max="4" width="21.09375" customWidth="1"/>
+    <col min="4" max="4" width="32.8125" customWidth="1"/>
     <col min="5" max="5" width="12.890625" customWidth="1"/>
     <col min="6" max="6" width="19.921875" customWidth="1"/>
     <col min="7" max="7" width="26.953125" customWidth="1"/>
     <col min="8" max="8" width="14.0625" customWidth="1"/>
     <col min="9" max="9" width="19.921875" customWidth="1"/>
+    <col min="10" max="10" width="15.234375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12042,6 +12049,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -12071,25 +12079,29 @@
       <c r="I2" s="4" t="s">
         <v>432</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -12099,25 +12111,28 @@
         <v>313</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="5">
@@ -12148,6 +12163,9 @@
       <c r="I5" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="J5" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="5" t="s">
@@ -12157,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E6" s="5">
         <v>20</v>
@@ -12171,10 +12189,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -12185,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E8" s="5">
         <v>40</v>
@@ -12199,10 +12217,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10">
@@ -12213,10 +12231,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11">
@@ -12227,7 +12245,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>336</v>
@@ -12244,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E12" s="5">
         <v>20</v>
@@ -12258,10 +12276,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14">
@@ -12272,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E14" s="5">
         <v>20</v>
@@ -12286,10 +12304,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -12300,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E16" s="5">
         <v>20</v>
@@ -12314,10 +12332,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18">
@@ -12328,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E18" s="5">
         <v>20</v>
@@ -12342,10 +12360,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20">
@@ -12356,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E20" s="5">
         <v>40</v>
@@ -12370,10 +12388,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22">
@@ -12384,10 +12402,10 @@
         <v>2</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23">
@@ -12398,7 +12416,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>336</v>
@@ -12415,7 +12433,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E24" s="5">
         <v>20</v>
@@ -12429,10 +12447,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26">
@@ -12443,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E26" s="5">
         <v>20</v>
@@ -12457,10 +12475,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28">
@@ -12471,7 +12489,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E28" s="5">
         <v>20</v>
@@ -12485,10 +12503,10 @@
         <v>1</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30">
@@ -12499,7 +12517,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E30" s="5">
         <v>40</v>
@@ -12513,10 +12531,10 @@
         <v>1</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32">
@@ -12527,10 +12545,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33">
@@ -12541,7 +12559,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>336</v>
@@ -12558,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E34" s="5">
         <v>20</v>
@@ -12572,10 +12590,10 @@
         <v>1</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36">
@@ -12586,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E36" s="5">
         <v>20</v>
@@ -12600,10 +12618,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38">
@@ -12614,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E38" s="5">
         <v>20</v>
@@ -12628,10 +12646,10 @@
         <v>1</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40">
@@ -12642,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E40" s="5">
         <v>40</v>
@@ -12656,10 +12674,10 @@
         <v>1</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42">
@@ -12670,10 +12688,10 @@
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43">
@@ -12684,7 +12702,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>336</v>
@@ -12701,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E44" s="5">
         <v>20</v>
@@ -12715,10 +12733,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46">
@@ -12729,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E46" s="5">
         <v>20</v>
@@ -12743,10 +12761,10 @@
         <v>1</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48">
@@ -12757,7 +12775,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E48" s="5">
         <v>20</v>
@@ -12771,10 +12789,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50">
@@ -12785,7 +12803,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E50" s="5">
         <v>20</v>
@@ -12799,10 +12817,10 @@
         <v>1</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52">
@@ -12813,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E52" s="5">
         <v>40</v>
@@ -12827,10 +12845,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54">
@@ -12841,10 +12859,10 @@
         <v>2</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="55">
@@ -12855,7 +12873,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>336</v>
@@ -12872,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E56" s="5">
         <v>20</v>
@@ -12886,10 +12904,10 @@
         <v>1</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58">
@@ -12900,7 +12918,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E58" s="5">
         <v>20</v>
@@ -12914,10 +12932,10 @@
         <v>1</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60">
@@ -12928,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E60" s="5">
         <v>20</v>
@@ -12942,10 +12960,10 @@
         <v>1</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62">
@@ -12956,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E62" s="5">
         <v>40</v>
@@ -12970,10 +12988,10 @@
         <v>1</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64">
@@ -12984,10 +13002,10 @@
         <v>2</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65">
@@ -12998,7 +13016,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>336</v>
@@ -13015,10 +13033,10 @@
         <v>0</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67">
@@ -13029,38 +13047,38 @@
         <v>0</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C68" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C69" s="6">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="70">
@@ -13068,41 +13086,41 @@
         <v>407</v>
       </c>
       <c r="C70" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
+      </c>
+      <c r="J70" s="5">
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C71" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C72" s="5">
         <v>0</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="73">
@@ -13110,41 +13128,41 @@
         <v>411</v>
       </c>
       <c r="C73" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
+      </c>
+      <c r="J73" s="6">
+        <v>40</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C74" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C75" s="6">
         <v>0</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="76">
@@ -13152,101 +13170,87 @@
         <v>415</v>
       </c>
       <c r="C76" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="I76" s="5" t="s">
         <v>453</v>
+      </c>
+      <c r="J76" s="5">
+        <v>60</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C77" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C78" s="5">
         <v>0</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="F78" s="5" t="s">
         <v>445</v>
+      </c>
+      <c r="E78" s="5">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C79" s="6">
         <v>0</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E79" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C80" s="5">
         <v>0</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E80" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C81" s="6">
         <v>0</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E81" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="C82" s="5">
-        <v>0</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E82" s="5">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I82"/>
+  <autoFilter ref="B2:J81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13265,10 +13269,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -13279,16 +13283,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
@@ -13299,13 +13303,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>308</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4">
@@ -13316,13 +13320,13 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5">
@@ -13344,10 +13348,10 @@
     </row>
     <row r="6">
       <c r="B6" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>13</v>
@@ -13358,10 +13362,10 @@
     </row>
     <row r="7">
       <c r="B7" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>13</v>
@@ -13372,10 +13376,10 @@
     </row>
     <row r="8">
       <c r="B8" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>467</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>465</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
@@ -13386,10 +13390,10 @@
     </row>
     <row r="9">
       <c r="B9" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>59</v>
@@ -13400,10 +13404,10 @@
     </row>
     <row r="10">
       <c r="B10" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>59</v>
@@ -13414,10 +13418,10 @@
     </row>
     <row r="11">
       <c r="B11" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>469</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>59</v>
@@ -13428,10 +13432,10 @@
     </row>
     <row r="12">
       <c r="B12" s="5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>105</v>
@@ -13442,10 +13446,10 @@
     </row>
     <row r="13">
       <c r="B13" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>105</v>
@@ -13456,10 +13460,10 @@
     </row>
     <row r="14">
       <c r="B14" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>105</v>
@@ -13470,10 +13474,10 @@
     </row>
     <row r="15">
       <c r="B15" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>151</v>
@@ -13484,10 +13488,10 @@
     </row>
     <row r="16">
       <c r="B16" s="5" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>151</v>
@@ -13498,10 +13502,10 @@
     </row>
     <row r="17">
       <c r="B17" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>479</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>151</v>
@@ -13512,10 +13516,10 @@
     </row>
     <row r="18">
       <c r="B18" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>197</v>
@@ -13526,10 +13530,10 @@
     </row>
     <row r="19">
       <c r="B19" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>197</v>
@@ -13540,10 +13544,10 @@
     </row>
     <row r="20">
       <c r="B20" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>483</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>481</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>197</v>

--- a/samples/wildling/design-data/xlsx/Reward.xlsx
+++ b/samples/wildling/design-data/xlsx/Reward.xlsx
@@ -11674,7 +11674,7 @@
         <v>329</v>
       </c>
       <c r="E375" s="6">
-        <v>240000</v>
+        <v>20000000</v>
       </c>
       <c r="G375" s="6" t="s">
         <v>331</v>
@@ -11697,7 +11697,7 @@
         <v>329</v>
       </c>
       <c r="E376" s="5">
-        <v>1200</v>
+        <v>90000</v>
       </c>
       <c r="G376" s="5" t="s">
         <v>333</v>
@@ -11720,7 +11720,7 @@
         <v>329</v>
       </c>
       <c r="E377" s="6">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="G377" s="6" t="s">
         <v>330</v>
@@ -11743,7 +11743,7 @@
         <v>325</v>
       </c>
       <c r="E378" s="5">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="F378" s="5" t="s">
         <v>326</v>
@@ -11766,7 +11766,7 @@
         <v>325</v>
       </c>
       <c r="E379" s="6">
-        <v>12</v>
+        <v>999</v>
       </c>
       <c r="F379" s="6" t="s">
         <v>327</v>
